--- a/inputs_raw_cases/cases_202512.xlsx
+++ b/inputs_raw_cases/cases_202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariellin1\Desktop\Case Complexity Index (CCI)\inputs_raw_cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariellin1\Desktop\Case Complexity Index (CCI)_V3\inputs_raw_cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233149F0-13BF-4DEF-B56D-B7D7B4ECE07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42766F4-7E26-4775-B0A3-47A1B35732F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8C551111-A817-4BCB-B4CF-B28DFACCC6A1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8C551111-A817-4BCB-B4CF-B28DFACCC6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -153,38 +153,12 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>松下銷售</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
       <t>是</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>板信商銀</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>FSA/</t>
     </r>
     <r>
@@ -201,40 +175,17 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>仁寶</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>遠雄人壽</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>宏碁</t>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>系統</t>
     </r>
     <r>
       <rPr>
@@ -243,23 +194,59 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Acer</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>系統</t>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>首查項目</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>健檢</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>否</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否首查</t>
     </r>
     <r>
       <rPr>
@@ -268,85 +255,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>首查項目</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>全國電子</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>GC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>健檢</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>中租控股</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>否</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否首查</t>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>或包含</t>
     </r>
     <r>
       <rPr>
@@ -355,17 +274,49 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>或包含</t>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>系統是否客製化</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>IPO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>送件類型</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否被</t>
     </r>
     <r>
       <rPr>
@@ -374,49 +325,20 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>系統是否客製化</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>IPO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>送件類型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否被</t>
+      <t>Q</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否為</t>
     </r>
     <r>
       <rPr>
@@ -425,11 +347,14 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Q</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
+      <t>PCAOB</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>IPO</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -438,6 +363,19 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
+      <t>是否為複雜資安</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
       <t>是否為</t>
     </r>
     <r>
@@ -459,24 +397,133 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否為複雜資安</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>IPO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否首查</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ITAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>題數</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ITAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否首查</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否首查</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Caats</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是否首查</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上櫃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>前底稿完整度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否為複雜資安</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否為</t>
+      </rPr>
+      <t>前期負責</t>
     </r>
     <r>
       <rPr>
@@ -485,178 +532,50 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>PCAOB</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>IPO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否為複雜資安</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>宇辰</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>IPO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否首查</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ITAC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>題數</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ITAC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否首查</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>GC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否首查</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Caats</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是否首查</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>上櫃</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>前底稿完整度</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
+      <t>PM</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="1"/>
-      </rPr>
-      <t>前期負責</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>PM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="1"/>
         <charset val="136"/>
       </rPr>
       <t>是否更換</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hh</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -696,13 +615,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="1"/>
       <charset val="136"/>
@@ -719,6 +631,12 @@
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="4"/>
     </font>
   </fonts>
   <fills count="6">
@@ -792,16 +710,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -813,16 +728,19 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1179,19 +1097,19 @@
     <col min="8" max="8" width="9.36328125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.81640625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="20.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.90625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="20.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1210,45 +1128,45 @@
         <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="N1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>34</v>
+      <c r="Q1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1260,37 +1178,37 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2">
         <f t="shared" ref="F2:F9" si="0">IF(E2="是",D2,"")</f>
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
+      <c r="A3" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -1299,28 +1217,28 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
+      <c r="A4" s="13" t="s">
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
@@ -1332,31 +1250,31 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1364,7 +1282,7 @@
       <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
@@ -1372,30 +1290,30 @@
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" s="8">
+        <v>9</v>
+      </c>
+      <c r="O5" s="7">
         <v>6</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
+      <c r="A6" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -1407,28 +1325,28 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="13" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
@@ -1440,37 +1358,37 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="8">
+        <v>13</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="7">
         <v>2</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="11" t="s">
-        <v>36</v>
+      <c r="Q7" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
+      <c r="A8" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1</v>
@@ -1482,28 +1400,28 @@
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>36</v>
+        <v>13</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
+      <c r="A9" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -1515,23 +1433,23 @@
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1645,32 +1563,32 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>25</v>
+      <c r="A7" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1691,18 +1609,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
-        <v>23</v>
+      <c r="A1" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>26</v>
+      <c r="A2" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="7" t="s">
-        <v>28</v>
+      <c r="A3" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1723,18 +1641,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="8" t="s">
-        <v>31</v>
+      <c r="A1" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="8" t="s">
-        <v>32</v>
+      <c r="A2" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="8" t="s">
-        <v>33</v>
+      <c r="A3" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1755,8 +1673,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="9" t="s">
-        <v>34</v>
+      <c r="A1" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
